--- a/backend/app/data/scheduling_data.xlsx
+++ b/backend/app/data/scheduling_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="78">
   <si>
     <r>
       <rPr>
@@ -103,12 +103,17 @@
     <t>27 Mar</t>
   </si>
   <si>
+    <r>
+      <t>12:00 AM</t>
+    </r>
+  </si>
+  <si>
+    <t>Shivani</t>
+  </si>
+  <si>
     <t>11:00 AM</t>
   </si>
   <si>
-    <t>Shivani</t>
-  </si>
-  <si>
     <t>Vishvani</t>
   </si>
   <si>
@@ -121,9 +126,7 @@
     <t>Priti</t>
   </si>
   <si>
-    <r>
-      <t>01:00 PM</t>
-    </r>
+    <t>01:00 PM</t>
   </si>
   <si>
     <t>Vaishnavi</t>
@@ -277,6 +280,12 @@
   </si>
   <si>
     <t>https://meet.google.com/onboardiq-kdd-ljtn</t>
+  </si>
+  <si>
+    <t>2026-03-31 10:40:56 UTC</t>
+  </si>
+  <si>
+    <t>https://meet.google.com/onboardiq-cff-awky</t>
   </si>
 </sst>
 </file>
@@ -892,7 +901,7 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>9</v>
@@ -917,7 +926,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
@@ -926,7 +935,7 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>9</v>
@@ -934,7 +943,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -951,7 +960,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
@@ -968,7 +977,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
@@ -985,16 +994,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
         <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>17</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>12</v>
@@ -1002,7 +1011,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
@@ -1014,12 +1023,12 @@
         <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
@@ -1036,7 +1045,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
@@ -1045,7 +1054,7 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>9</v>
@@ -1053,13 +1062,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -1070,7 +1079,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
@@ -1079,7 +1088,7 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -1087,7 +1096,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
         <v>6</v>
@@ -1104,7 +1113,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
         <v>6</v>
@@ -1121,13 +1130,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
         <v>22</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>21</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
@@ -1138,7 +1147,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
@@ -1155,7 +1164,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
@@ -1164,7 +1173,7 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>9</v>
@@ -1172,13 +1181,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -1189,13 +1198,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
@@ -1206,7 +1215,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
@@ -1223,13 +1232,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
         <v>8</v>
@@ -1240,16 +1249,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>9</v>
@@ -1257,10 +1266,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
@@ -1274,10 +1283,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
@@ -1291,16 +1300,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>12</v>
@@ -1308,10 +1317,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
         <v>16</v>
@@ -1325,10 +1334,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
         <v>16</v>
@@ -1342,10 +1351,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
         <v>7</v>
@@ -1359,10 +1368,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
         <v>7</v>
@@ -1376,10 +1385,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
@@ -1393,10 +1402,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
         <v>15</v>
@@ -1410,16 +1419,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
         <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>9</v>
@@ -1427,10 +1436,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -1444,10 +1453,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -1461,10 +1470,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
         <v>16</v>
@@ -1478,16 +1487,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
         <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>12</v>
@@ -1495,16 +1504,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>12</v>
@@ -1512,10 +1521,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
@@ -1529,10 +1538,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
         <v>16</v>
@@ -1546,16 +1555,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>12</v>
@@ -1563,10 +1572,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
         <v>16</v>
@@ -1580,16 +1589,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
         <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>12</v>
@@ -1597,13 +1606,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -1614,13 +1623,13 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
@@ -1631,10 +1640,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
         <v>16</v>
@@ -1648,13 +1657,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
@@ -1665,16 +1674,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>12</v>
@@ -1682,10 +1691,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
         <v>7</v>
@@ -1699,16 +1708,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C62" t="s">
         <v>7</v>
       </c>
       <c r="D62" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>12</v>
@@ -1716,10 +1725,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
         <v>15</v>
@@ -1733,10 +1742,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C64" t="s">
         <v>16</v>
@@ -1750,16 +1759,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C65" t="s">
         <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>12</v>
@@ -1767,10 +1776,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
@@ -1784,10 +1793,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
         <v>15</v>
@@ -1801,16 +1810,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C68" t="s">
         <v>16</v>
       </c>
       <c r="D68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>9</v>
@@ -1818,16 +1827,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C69" t="s">
         <v>7</v>
       </c>
       <c r="D69" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>9</v>
@@ -1835,10 +1844,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B70" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C70" t="s">
         <v>15</v>
@@ -1852,10 +1861,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C71" t="s">
         <v>15</v>
@@ -1869,16 +1878,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C72" t="s">
         <v>16</v>
       </c>
       <c r="D72" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>9</v>
@@ -1886,13 +1895,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D73" t="s">
         <v>10</v>
@@ -1903,10 +1912,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" t="s">
         <v>37</v>
-      </c>
-      <c r="B74" t="s">
-        <v>36</v>
       </c>
       <c r="C74" t="s">
         <v>7</v>
@@ -1920,16 +1929,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" t="s">
         <v>37</v>
       </c>
-      <c r="B75" t="s">
-        <v>36</v>
-      </c>
       <c r="C75" t="s">
         <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>9</v>
@@ -1937,10 +1946,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" t="s">
         <v>37</v>
-      </c>
-      <c r="B76" t="s">
-        <v>36</v>
       </c>
       <c r="C76" t="s">
         <v>16</v>
@@ -1954,10 +1963,10 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" t="s">
         <v>37</v>
-      </c>
-      <c r="B77" t="s">
-        <v>36</v>
       </c>
       <c r="C77" t="s">
         <v>16</v>
@@ -1971,10 +1980,10 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C78" t="s">
         <v>15</v>
@@ -1988,10 +1997,10 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -2005,10 +2014,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C80" t="s">
         <v>16</v>
@@ -2022,16 +2031,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D81" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>9</v>
@@ -2039,10 +2048,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C82" t="s">
         <v>15</v>
@@ -2056,10 +2065,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B83" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C83" t="s">
         <v>16</v>
@@ -2073,10 +2082,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C84" t="s">
         <v>16</v>
@@ -2090,13 +2099,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B85" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D85" t="s">
         <v>8</v>
@@ -2107,16 +2116,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C86" t="s">
         <v>16</v>
       </c>
       <c r="D86" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>12</v>
@@ -2124,13 +2133,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D87" t="s">
         <v>8</v>
@@ -2141,13 +2150,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D88" t="s">
         <v>13</v>
@@ -2158,16 +2167,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>12</v>
@@ -2183,7 +2192,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2199,77 +2208,77 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -2278,33 +2287,33 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -2313,30 +2322,30 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -2345,144 +2354,176 @@
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
         <v>55</v>
       </c>
-      <c r="I9" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" t="s">
-        <v>74</v>
+      <c r="H10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/backend/app/data/scheduling_data.xlsx
+++ b/backend/app/data/scheduling_data.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2989,6 +2989,110 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anurag Mandlekar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Manager Introduction</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prathamesh</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>26 Mar</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-04-03 06:06:35 UTC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://meet.google.com/onboardiq-qir-rfev</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mughda</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HR Introduction</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mohini</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25 Mar</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>09:00 AM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-04-03 10:39:08 UTC</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://meet.google.com/onboardiq-udc-hanb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
